--- a/tests/regression_artifacts/downloads/email_03152025_Free_returns_within_90_days/current/None.xlsx
+++ b/tests/regression_artifacts/downloads/email_03152025_Free_returns_within_90_days/current/None.xlsx
@@ -781,14 +781,14 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>64031900</t>
+          <t>64041990</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>64031900</t>
+          <t>64041990</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -868,7 +868,7 @@
       <c r="AJ2" s="2" t="n"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>64031900</t>
+          <t>64041990</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>64031900</t>
+          <t>64041990</t>
         </is>
       </c>
       <c r="G3" s="4" t="n"/>
@@ -1944,7 +1944,7 @@
       <c r="I28" s="15" t="n"/>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>CET (weighted avg 15.5%)</t>
+          <t>CET (weighted avg 20.0%)</t>
         </is>
       </c>
       <c r="K28" s="15" t="n"/>
@@ -1953,7 +1953,7 @@
       <c r="N28" s="15" t="n"/>
       <c r="O28" s="15" t="n"/>
       <c r="P28" s="17" t="n">
-        <v>7.5</v>
+        <v>9.67</v>
       </c>
       <c r="Q28" s="15" t="n"/>
       <c r="R28" s="15" t="n"/>
@@ -1989,7 +1989,7 @@
       <c r="I29" s="15" t="n"/>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 64031900: 10% CET (45% of value)</t>
+          <t xml:space="preserve">  └ 64041990: 20% CET (45% of value)</t>
         </is>
       </c>
       <c r="K29" s="15" t="n"/>
@@ -1998,7 +1998,7 @@
       <c r="N29" s="15" t="n"/>
       <c r="O29" s="15" t="n"/>
       <c r="P29" s="17" t="n">
-        <v>2.17</v>
+        <v>4.34</v>
       </c>
       <c r="Q29" s="15" t="n"/>
       <c r="R29" s="15" t="n"/>
@@ -2178,7 +2178,7 @@
       <c r="N33" s="15" t="n"/>
       <c r="O33" s="15" t="n"/>
       <c r="P33" s="17" t="n">
-        <v>8.81</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="Q33" s="15" t="n"/>
       <c r="R33" s="15" t="n"/>
@@ -2223,7 +2223,7 @@
       <c r="N34" s="18" t="n"/>
       <c r="O34" s="18" t="n"/>
       <c r="P34" s="19" t="n">
-        <v>19.21</v>
+        <v>21.7</v>
       </c>
       <c r="Q34" s="18" t="n"/>
       <c r="R34" s="18" t="n"/>
@@ -2268,7 +2268,7 @@
       <c r="N35" s="15" t="n"/>
       <c r="O35" s="15" t="n"/>
       <c r="P35" s="20" t="n">
-        <v>0.3974756879784813</v>
+        <v>0.4489964825160356</v>
       </c>
       <c r="Q35" s="15" t="n"/>
       <c r="R35" s="15" t="n"/>
@@ -2358,7 +2358,7 @@
       <c r="N37" s="15" t="n"/>
       <c r="O37" s="15" t="n"/>
       <c r="P37" s="22" t="n">
-        <v>2004.79</v>
+        <v>2002.3</v>
       </c>
       <c r="Q37" s="15" t="n"/>
       <c r="R37" s="15" t="n"/>
@@ -2394,7 +2394,7 @@
       <c r="I38" s="15" t="n"/>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>IMPLIED CIF (from declared duty @ 16% CET, XCD)</t>
+          <t>IMPLIED CIF (from declared duty @ 20% CET, XCD)</t>
         </is>
       </c>
       <c r="K38" s="15" t="n"/>
@@ -2403,7 +2403,7 @@
       <c r="N38" s="15" t="n"/>
       <c r="O38" s="15" t="n"/>
       <c r="P38" s="17" t="n">
-        <v>5093.74</v>
+        <v>4507.8</v>
       </c>
       <c r="Q38" s="15" t="n"/>
       <c r="R38" s="15" t="n"/>
@@ -2448,7 +2448,7 @@
       <c r="N39" s="15" t="n"/>
       <c r="O39" s="15" t="n"/>
       <c r="P39" s="17" t="n">
-        <v>1874.84</v>
+        <v>1659.17</v>
       </c>
       <c r="Q39" s="15" t="n"/>
       <c r="R39" s="15" t="n"/>
@@ -2484,7 +2484,7 @@
       <c r="I40" s="15" t="n"/>
       <c r="J40" s="21" t="inlineStr">
         <is>
-          <t>⚠ ITEM ALLOCATION CHECK: actual $17.79 USD vs implied $1,874.84 USD — UNDER-ALLOCATED (items from another waybill may belong here)</t>
+          <t>⚠ ITEM ALLOCATION CHECK: actual $17.79 USD vs implied $1,659.17 USD — UNDER-ALLOCATED (items from another waybill may belong here)</t>
         </is>
       </c>
       <c r="K40" s="15" t="n"/>
